--- a/Data/EXCEL/Transfer/salemon/202512/7820-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7820-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC06DBE-0430-4427-B768-DA07C5290274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B9DAF88-D755-4A44-8CB0-576207A8789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{FBCD4174-2108-4D8E-B5EA-660359E67356}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{6D196A9D-3CFD-4B47-A259-37A0E555AB5E}"/>
   </bookViews>
   <sheets>
     <sheet name="7820-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -1258,21 +1258,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC2C0B2-07F0-4974-B610-1B64DD4C5A8E}">
-  <dimension ref="A1:Q16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0308B11-452A-4E77-88C6-A456079DD132}">
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="7.875" customWidth="1"/>
+    <col min="9" max="9" width="7.5" customWidth="1"/>
+    <col min="10" max="13" width="7.875" customWidth="1"/>
+    <col min="14" max="14" width="7.5" customWidth="1"/>
+    <col min="15" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1425,484 +1425,484 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C5" s="6">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D5" s="6">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E5" s="6">
-        <v>131.5</v>
+        <v>145.5</v>
       </c>
       <c r="F5" s="7">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="G5" s="7">
-        <v>-9.9</v>
+        <v>-12.14</v>
       </c>
       <c r="H5" s="8">
-        <v>0.221</v>
-      </c>
-      <c r="I5" s="7">
-        <v>-23</v>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I5" s="9">
+        <v>51.4</v>
       </c>
       <c r="J5" s="9">
-        <v>6.89</v>
+        <v>59.2</v>
       </c>
       <c r="K5" s="8">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="L5" s="9">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="M5" s="8">
-        <v>0.221</v>
-      </c>
-      <c r="N5" s="7">
-        <v>-23</v>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="N5" s="9">
+        <v>51.4</v>
       </c>
       <c r="O5" s="9">
-        <v>6.89</v>
+        <v>59.2</v>
       </c>
       <c r="P5" s="8">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="Q5" s="9">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C6" s="12">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="D6" s="12">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="E6" s="12">
-        <v>188.5</v>
+        <v>131.5</v>
       </c>
       <c r="F6" s="13">
-        <v>-4</v>
+        <v>-19</v>
       </c>
       <c r="G6" s="13">
-        <v>-2.04</v>
+        <v>-9.9</v>
       </c>
       <c r="H6" s="14">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="I6" s="15">
-        <v>14.2</v>
+        <v>0.221</v>
+      </c>
+      <c r="I6" s="13">
+        <v>-23</v>
       </c>
       <c r="J6" s="15">
-        <v>13.5</v>
+        <v>6.89</v>
       </c>
       <c r="K6" s="14">
-        <v>2.4300000000000002</v>
+        <v>2.65</v>
       </c>
       <c r="L6" s="15">
-        <v>65.8</v>
+        <v>58.5</v>
       </c>
       <c r="M6" s="14">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="N6" s="15">
-        <v>14.2</v>
+        <v>0.221</v>
+      </c>
+      <c r="N6" s="13">
+        <v>-23</v>
       </c>
       <c r="O6" s="15">
-        <v>13.5</v>
+        <v>6.89</v>
       </c>
       <c r="P6" s="14">
-        <v>2.4300000000000002</v>
+        <v>2.65</v>
       </c>
       <c r="Q6" s="15">
-        <v>65.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="C7" s="6">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D7" s="6">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="E7" s="6">
-        <v>180.5</v>
+        <v>188.5</v>
       </c>
       <c r="F7" s="7">
-        <v>-52</v>
+        <v>-4</v>
       </c>
       <c r="G7" s="7">
-        <v>-20.97</v>
+        <v>-2.04</v>
       </c>
       <c r="H7" s="8">
-        <v>0.251</v>
-      </c>
-      <c r="I7" s="7">
-        <v>-8.2799999999999994</v>
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="I7" s="9">
+        <v>14.2</v>
       </c>
       <c r="J7" s="9">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="K7" s="8">
-        <v>2.14</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="L7" s="9">
-        <v>76.8</v>
+        <v>65.8</v>
       </c>
       <c r="M7" s="8">
-        <v>0.251</v>
-      </c>
-      <c r="N7" s="7">
-        <v>-8.2799999999999994</v>
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="N7" s="9">
+        <v>14.2</v>
       </c>
       <c r="O7" s="9">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="P7" s="8">
-        <v>2.14</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="Q7" s="9">
-        <v>76.8</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="C8" s="12">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="D8" s="12">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E8" s="12">
-        <v>182</v>
-      </c>
-      <c r="F8" s="15">
-        <v>53</v>
-      </c>
-      <c r="G8" s="15">
-        <v>27.18</v>
+        <v>180.5</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-52</v>
+      </c>
+      <c r="G8" s="13">
+        <v>-20.97</v>
       </c>
       <c r="H8" s="14">
-        <v>0.27400000000000002</v>
+        <v>0.251</v>
       </c>
       <c r="I8" s="13">
-        <v>-1.25</v>
+        <v>-8.2799999999999994</v>
       </c>
       <c r="J8" s="15">
-        <v>23.8</v>
+        <v>35.4</v>
       </c>
       <c r="K8" s="14">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="L8" s="15">
-        <v>84.2</v>
+        <v>76.8</v>
       </c>
       <c r="M8" s="14">
-        <v>0.27400000000000002</v>
+        <v>0.251</v>
       </c>
       <c r="N8" s="13">
-        <v>-1.25</v>
+        <v>-8.2799999999999994</v>
       </c>
       <c r="O8" s="15">
-        <v>23.8</v>
+        <v>35.4</v>
       </c>
       <c r="P8" s="14">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" s="15">
-        <v>84.2</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="C9" s="6">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="D9" s="6">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="E9" s="6">
-        <v>149.5</v>
+        <v>182</v>
       </c>
       <c r="F9" s="9">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G9" s="9">
-        <v>25</v>
+        <v>27.18</v>
       </c>
       <c r="H9" s="8">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="I9" s="9">
-        <v>8.27</v>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I9" s="7">
+        <v>-1.25</v>
       </c>
       <c r="J9" s="9">
-        <v>77.3</v>
+        <v>23.8</v>
       </c>
       <c r="K9" s="8">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="L9" s="9">
-        <v>100.9</v>
+        <v>84.2</v>
       </c>
       <c r="M9" s="8">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="N9" s="9">
-        <v>8.27</v>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="N9" s="7">
+        <v>-1.25</v>
       </c>
       <c r="O9" s="9">
-        <v>77.3</v>
+        <v>23.8</v>
       </c>
       <c r="P9" s="8">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" s="9">
-        <v>100.9</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>80.7</v>
+        <v>156</v>
       </c>
       <c r="C10" s="12">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="D10" s="12">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="E10" s="12">
-        <v>79</v>
+        <v>149.5</v>
       </c>
       <c r="F10" s="15">
-        <v>75.3</v>
+        <v>39</v>
       </c>
       <c r="G10" s="15">
-        <v>93.31</v>
+        <v>25</v>
       </c>
       <c r="H10" s="14">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="I10" s="13">
-        <v>-4.83</v>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="I10" s="15">
+        <v>8.27</v>
       </c>
       <c r="J10" s="15">
-        <v>98.2</v>
+        <v>77.3</v>
       </c>
       <c r="K10" s="14">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="L10" s="15">
-        <v>106.6</v>
+        <v>100.9</v>
       </c>
       <c r="M10" s="14">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="N10" s="13">
-        <v>-4.83</v>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="N10" s="15">
+        <v>8.27</v>
       </c>
       <c r="O10" s="15">
-        <v>98.2</v>
+        <v>77.3</v>
       </c>
       <c r="P10" s="14">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" s="15">
-        <v>106.6</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>78.099999999999994</v>
+        <v>80.7</v>
       </c>
       <c r="C11" s="6">
-        <v>80.7</v>
+        <v>156</v>
       </c>
       <c r="D11" s="6">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="E11" s="6">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" s="9">
-        <v>2.6</v>
+        <v>75.3</v>
       </c>
       <c r="G11" s="9">
-        <v>3.33</v>
+        <v>93.31</v>
       </c>
       <c r="H11" s="8">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="I11" s="9">
-        <v>26.9</v>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="I11" s="7">
+        <v>-4.83</v>
       </c>
       <c r="J11" s="9">
-        <v>124.8</v>
+        <v>98.2</v>
       </c>
       <c r="K11" s="8">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="L11" s="9">
-        <v>108.7</v>
+        <v>106.6</v>
       </c>
       <c r="M11" s="8">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="N11" s="9">
-        <v>26.9</v>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="N11" s="7">
+        <v>-4.83</v>
       </c>
       <c r="O11" s="9">
-        <v>124.8</v>
+        <v>98.2</v>
       </c>
       <c r="P11" s="8">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="Q11" s="9">
-        <v>108.7</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>90.9</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="C12" s="12">
-        <v>78.099999999999994</v>
+        <v>80.7</v>
       </c>
       <c r="D12" s="12">
-        <v>95.9</v>
+        <v>82</v>
       </c>
       <c r="E12" s="12">
-        <v>60.2</v>
-      </c>
-      <c r="F12" s="13">
-        <v>-12.8</v>
-      </c>
-      <c r="G12" s="13">
-        <v>-14.08</v>
+        <v>76</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2.6</v>
+      </c>
+      <c r="G12" s="15">
+        <v>3.33</v>
       </c>
       <c r="H12" s="14">
-        <v>0.21199999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="I12" s="15">
-        <v>4.2699999999999996</v>
+        <v>26.9</v>
       </c>
       <c r="J12" s="15">
-        <v>102.9</v>
+        <v>124.8</v>
       </c>
       <c r="K12" s="14">
-        <v>0.81200000000000006</v>
+        <v>1.08</v>
       </c>
       <c r="L12" s="15">
-        <v>103.8</v>
+        <v>108.7</v>
       </c>
       <c r="M12" s="14">
-        <v>0.21199999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="N12" s="15">
-        <v>4.2699999999999996</v>
+        <v>26.9</v>
       </c>
       <c r="O12" s="15">
-        <v>102.9</v>
+        <v>124.8</v>
       </c>
       <c r="P12" s="14">
-        <v>0.81200000000000006</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" s="15">
-        <v>103.8</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>17</v>
+        <v>45748</v>
+      </c>
+      <c r="B13" s="6">
+        <v>90.9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="D13" s="6">
+        <v>95.9</v>
+      </c>
+      <c r="E13" s="6">
+        <v>60.2</v>
+      </c>
+      <c r="F13" s="7">
+        <v>-12.8</v>
+      </c>
+      <c r="G13" s="7">
+        <v>-14.08</v>
       </c>
       <c r="H13" s="8">
-        <v>0.20399999999999999</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="I13" s="9">
-        <v>3.74</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="J13" s="9">
-        <v>110.5</v>
+        <v>102.9</v>
       </c>
       <c r="K13" s="8">
-        <v>0.6</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="L13" s="9">
-        <v>104.1</v>
+        <v>103.8</v>
       </c>
       <c r="M13" s="8">
-        <v>0.20399999999999999</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="N13" s="9">
-        <v>3.74</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="O13" s="9">
-        <v>110.5</v>
+        <v>102.9</v>
       </c>
       <c r="P13" s="8">
-        <v>0.6</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="Q13" s="9">
-        <v>104.1</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>17</v>
@@ -1923,39 +1923,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="14">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="I14" s="13">
-        <v>-1.74</v>
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="I14" s="15">
+        <v>3.74</v>
       </c>
       <c r="J14" s="15">
-        <v>110.8</v>
+        <v>110.5</v>
       </c>
       <c r="K14" s="14">
-        <v>0.39600000000000002</v>
+        <v>0.6</v>
       </c>
       <c r="L14" s="15">
-        <v>101</v>
+        <v>104.1</v>
       </c>
       <c r="M14" s="14">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="N14" s="13">
-        <v>-1.74</v>
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="N14" s="15">
+        <v>3.74</v>
       </c>
       <c r="O14" s="15">
-        <v>110.8</v>
+        <v>110.5</v>
       </c>
       <c r="P14" s="14">
-        <v>0.39600000000000002</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" s="15">
-        <v>101</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>17</v>
@@ -1976,86 +1976,139 @@
         <v>17</v>
       </c>
       <c r="H15" s="8">
-        <v>0.2</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="I15" s="7">
-        <v>-4.9800000000000004</v>
+        <v>-1.74</v>
       </c>
       <c r="J15" s="9">
-        <v>92.2</v>
+        <v>110.8</v>
       </c>
       <c r="K15" s="8">
-        <v>0.2</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="L15" s="9">
-        <v>92.2</v>
+        <v>101</v>
       </c>
       <c r="M15" s="8">
-        <v>0.2</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="N15" s="7">
-        <v>-4.9800000000000004</v>
+        <v>-1.74</v>
       </c>
       <c r="O15" s="9">
-        <v>92.2</v>
+        <v>110.8</v>
       </c>
       <c r="P15" s="8">
-        <v>0.2</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="Q15" s="9">
-        <v>92.2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
+        <v>45658</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="I16" s="13">
+        <v>-4.9800000000000004</v>
+      </c>
+      <c r="J16" s="15">
+        <v>92.2</v>
+      </c>
+      <c r="K16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="15">
+        <v>92.2</v>
+      </c>
+      <c r="M16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="13">
+        <v>-4.9800000000000004</v>
+      </c>
+      <c r="O16" s="15">
+        <v>92.2</v>
+      </c>
+      <c r="P16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>45627</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="8">
         <v>0.21</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="I17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="9">
         <v>173.6</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K17" s="8">
         <v>1.88</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L17" s="9">
         <v>9</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M17" s="8">
         <v>0.21</v>
       </c>
-      <c r="N16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O16" s="15">
+      <c r="N17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O17" s="9">
         <v>173.6</v>
       </c>
-      <c r="P16" s="14">
+      <c r="P17" s="8">
         <v>1.88</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q17" s="9">
         <v>9</v>
       </c>
     </row>
